--- a/GroceryApplicationProject/src/test/resources/TestData.xlsx
+++ b/GroceryApplicationProject/src/test/resources/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SREE_ECLIPSE_WORKSPACE\GroceryApplicationProject\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj\git\GroceryApplicationProjectRepository\GroceryApplicationProject\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA0197E-F575-47D9-925F-745A0F760796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DF6419-0C42-4AD9-B7CD-9E98B140312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>admin</t>
   </si>
@@ -50,6 +50,18 @@
   </si>
   <si>
     <t>Delivery Boy</t>
+  </si>
+  <si>
+    <t>admin6</t>
+  </si>
+  <si>
+    <t>admin8</t>
+  </si>
+  <si>
+    <t>pswd</t>
+  </si>
+  <si>
+    <t>pswd2</t>
   </si>
 </sst>
 </file>
@@ -388,18 +400,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
